--- a/tasks/finalpool/howtocook-playwright-price/groundtruth_workspace/Recipe_Cost_Analysis.xlsx
+++ b/tasks/finalpool/howtocook-playwright-price/groundtruth_workspace/Recipe_Cost_Analysis.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dish Costs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ingredient Prices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,113 +421,113 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Dish Name</t>
+          <t>Dish_Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Ingredient_List</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ingredient Count</t>
+          <t>Estimated_Total_Cost</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Estimated Cost</t>
+          <t>Cost_Per_Serving</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>可乐鸡翅</t>
+          <t>Cola Chicken Wings</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>荤菜</t>
+          <t>Chicken Wings, Cola, Soy Sauce, Ginger, Garlic, Star Anise</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>水煮鱼</t>
+          <t>Boiled Fish</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>水产</t>
+          <t>Fish, Sichuan Pepper, Chili, Ginger, Garlic, Sprouts, Soybean Paste, Egg</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>35</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>凉拌金针菇</t>
+          <t>Cold Enoki Mushroom</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>素菜</t>
+          <t>Enoki Mushroom, Sesame Oil, Garlic, Soy Sauce, Vinegar</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>炒年糕</t>
+          <t>Stir-Fried Rice Cake</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>主食</t>
+          <t>Rice Cake, Cabbage, Soy Sauce, Sugar, Ginger, Garlic</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>奶油蘑菇汤</t>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>汤</t>
+          <t>Mushrooms, Cream, Onion, Butter, Flour, Stock, Salt</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -540,248 +541,338 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Ingredient</t>
+          <t>Ingredient_Name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Price Per Unit</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Price_Per_Unit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Source_Dish</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>鸡翅</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+          <t>Chicken Wings</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>15</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>500g</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cola Chicken Wings</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>可乐</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+          <t>Cola</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500ml</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>5</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>500ml</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Cola Chicken Wings</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>金针菇</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>150g</t>
+          <t>Fish</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Boiled Fish</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>年糕</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>250g</t>
+          <t>Enoki Mushroom</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150g</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Cold Enoki Mushroom</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>白蘑菇</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>200g</t>
+          <t>Rice Cake</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stir-Fried Rice Cake</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>巴沙鱼</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>25</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>500g</t>
+          <t>Mushrooms</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>200g</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>洋葱</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>500g</t>
+          <t>Cream</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>200ml</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>黄油</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>100g</t>
+          <t>Onion</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>牛奶</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1L</t>
+          <t>Butter</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>200g</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>酱油</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>500ml</t>
+          <t>Flour</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>500g</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>面粉</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1L</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>500g</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Cream Mushroom Soup</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>食用油</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1L</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>生姜</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" t="inlineStr">
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>大蒜</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>100g</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>淡奶油</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>18</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>200ml</t>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cola Chicken Wings, Boiled Fish, Cold Enoki Mushroom</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total_Cost</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Average_Cost_Per_Dish</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cheapest_Dish</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cold Enoki Mushroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Most_Expensive_Dish</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Boiled Fish</t>
         </is>
       </c>
     </row>
